--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/107.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/107.xlsx
@@ -426,13 +426,13 @@
         <v>-11.66472361706667</v>
       </c>
       <c r="E2">
-        <v>-9.57692306303105</v>
+        <v>-9.939051544002426</v>
       </c>
       <c r="F2">
-        <v>-4.172469359433158</v>
+        <v>-4.031897896280291</v>
       </c>
       <c r="G2">
-        <v>-10.17718755222072</v>
+        <v>-9.298466139186427</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.19906601912852</v>
       </c>
       <c r="E3">
-        <v>-10.40377713209158</v>
+        <v>-10.04533482896245</v>
       </c>
       <c r="F3">
-        <v>-4.297827855233614</v>
+        <v>-4.28806803049383</v>
       </c>
       <c r="G3">
-        <v>-9.493947232189312</v>
+        <v>-9.011408735476223</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.64697767888049</v>
       </c>
       <c r="E4">
-        <v>-10.78578108548262</v>
+        <v>-10.25209136673065</v>
       </c>
       <c r="F4">
-        <v>-3.927339705964132</v>
+        <v>-3.953979173270761</v>
       </c>
       <c r="G4">
-        <v>-9.448599379392375</v>
+        <v>-9.481648555510919</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.04983576108355</v>
       </c>
       <c r="E5">
-        <v>-11.43463895519766</v>
+        <v>-10.98356671624163</v>
       </c>
       <c r="F5">
-        <v>-4.362082657933966</v>
+        <v>-4.38389440001708</v>
       </c>
       <c r="G5">
-        <v>-9.353348363136465</v>
+        <v>-8.984712496247539</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.39824145531002</v>
       </c>
       <c r="E6">
-        <v>-12.41105946378353</v>
+        <v>-12.06514291975961</v>
       </c>
       <c r="F6">
-        <v>-4.386229567725572</v>
+        <v>-4.514271145543693</v>
       </c>
       <c r="G6">
-        <v>-8.514181348205387</v>
+        <v>-8.572662135156612</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.69301847635791</v>
       </c>
       <c r="E7">
-        <v>-12.6541071922492</v>
+        <v>-12.73678354220724</v>
       </c>
       <c r="F7">
-        <v>-4.719788269810848</v>
+        <v>-4.530607379094302</v>
       </c>
       <c r="G7">
-        <v>-8.833993289481141</v>
+        <v>-8.390135206848894</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.937040171546431</v>
       </c>
       <c r="E8">
-        <v>-13.72094321287222</v>
+        <v>-14.04395926383934</v>
       </c>
       <c r="F8">
-        <v>-4.302600079841142</v>
+        <v>-4.439727191333168</v>
       </c>
       <c r="G8">
-        <v>-8.058491375815786</v>
+        <v>-8.154834872099656</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.129080467724855</v>
       </c>
       <c r="E9">
-        <v>-14.83263376854121</v>
+        <v>-15.12895899370712</v>
       </c>
       <c r="F9">
-        <v>-4.636714616453697</v>
+        <v>-4.364037605004572</v>
       </c>
       <c r="G9">
-        <v>-8.175909805002657</v>
+        <v>-8.126807793564186</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.281650592503493</v>
       </c>
       <c r="E10">
-        <v>-14.7885898303426</v>
+        <v>-15.2134874895343</v>
       </c>
       <c r="F10">
-        <v>-4.716115288746835</v>
+        <v>-4.87815057967364</v>
       </c>
       <c r="G10">
-        <v>-7.466337405751888</v>
+        <v>-7.718402343111997</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.400963554119772</v>
       </c>
       <c r="E11">
-        <v>-16.49797102791397</v>
+        <v>-16.4425560914821</v>
       </c>
       <c r="F11">
-        <v>-4.854198336221693</v>
+        <v>-4.707955041461857</v>
       </c>
       <c r="G11">
-        <v>-6.281804348527422</v>
+        <v>-6.798338837383287</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.514266197796267</v>
       </c>
       <c r="E12">
-        <v>-16.65242369089358</v>
+        <v>-16.72941227749798</v>
       </c>
       <c r="F12">
-        <v>-4.884413037238805</v>
+        <v>-4.791927473451046</v>
       </c>
       <c r="G12">
-        <v>-6.337087148487711</v>
+        <v>-6.028521130408862</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.643681200108496</v>
       </c>
       <c r="E13">
-        <v>-18.14225541162507</v>
+        <v>-18.03698650484276</v>
       </c>
       <c r="F13">
-        <v>-4.406943722999975</v>
+        <v>-4.638488151063091</v>
       </c>
       <c r="G13">
-        <v>-5.544780905665017</v>
+        <v>-5.627484954327089</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.834590673489513</v>
       </c>
       <c r="E14">
-        <v>-17.77509126755716</v>
+        <v>-17.45691162683022</v>
       </c>
       <c r="F14">
-        <v>-4.623282639017303</v>
+        <v>-4.167712045438881</v>
       </c>
       <c r="G14">
-        <v>-5.856621053282206</v>
+        <v>-5.264354524669972</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.129223648644098</v>
       </c>
       <c r="E15">
-        <v>-19.56604839590269</v>
+        <v>-19.00139297188628</v>
       </c>
       <c r="F15">
-        <v>-4.411112067770863</v>
+        <v>-4.499878261920053</v>
       </c>
       <c r="G15">
-        <v>-4.519134171052332</v>
+        <v>-4.740189228346087</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.577430102164642</v>
       </c>
       <c r="E16">
-        <v>-20.49612450149406</v>
+        <v>-19.87063808613261</v>
       </c>
       <c r="F16">
-        <v>-4.193330964105262</v>
+        <v>-4.207027190743148</v>
       </c>
       <c r="G16">
-        <v>-3.940950703164158</v>
+        <v>-4.169768989747504</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.219775591121423</v>
       </c>
       <c r="E17">
-        <v>-22.07479129683402</v>
+        <v>-20.88325015898778</v>
       </c>
       <c r="F17">
-        <v>-4.2147947918792</v>
+        <v>-4.277165058738182</v>
       </c>
       <c r="G17">
-        <v>-4.112231708274971</v>
+        <v>-3.948432536082911</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.083497005623659</v>
       </c>
       <c r="E18">
-        <v>-21.58831997656003</v>
+        <v>-21.83605920409765</v>
       </c>
       <c r="F18">
-        <v>-3.575563547956488</v>
+        <v>-3.363717696731945</v>
       </c>
       <c r="G18">
-        <v>-3.622211378643128</v>
+        <v>-4.085313662495157</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.181722340119799</v>
       </c>
       <c r="E19">
-        <v>-22.85295521336408</v>
+        <v>-22.59261777113711</v>
       </c>
       <c r="F19">
-        <v>-3.532548085463915</v>
+        <v>-3.419236536802374</v>
       </c>
       <c r="G19">
-        <v>-3.643160510815636</v>
+        <v>-3.611577906370989</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.505670344657816</v>
       </c>
       <c r="E20">
-        <v>-24.40038912347313</v>
+        <v>-23.37338556022159</v>
       </c>
       <c r="F20">
-        <v>-3.156109773140125</v>
+        <v>-3.294771021062137</v>
       </c>
       <c r="G20">
-        <v>-3.699297431525058</v>
+        <v>-3.336001474590977</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.034658777868693</v>
       </c>
       <c r="E21">
-        <v>-24.72621735679902</v>
+        <v>-23.93761983615529</v>
       </c>
       <c r="F21">
-        <v>-2.922917722312842</v>
+        <v>-2.757785165666969</v>
       </c>
       <c r="G21">
-        <v>-3.946174744025128</v>
+        <v>-3.622651681199851</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.726490504493211</v>
       </c>
       <c r="E22">
-        <v>-25.22650505127041</v>
+        <v>-24.04588659273067</v>
       </c>
       <c r="F22">
-        <v>-2.406178822976899</v>
+        <v>-2.442775266465178</v>
       </c>
       <c r="G22">
-        <v>-4.355778611962534</v>
+        <v>-3.5709210966032</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.532677401771997</v>
       </c>
       <c r="E23">
-        <v>-26.20194740947062</v>
+        <v>-26.56221921609885</v>
       </c>
       <c r="F23">
-        <v>-2.368850931071948</v>
+        <v>-2.269015263319148</v>
       </c>
       <c r="G23">
-        <v>-3.683681588216316</v>
+        <v>-3.851784469609428</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.391849059379985</v>
       </c>
       <c r="E24">
-        <v>-26.31292219350259</v>
+        <v>-26.21776989765342</v>
       </c>
       <c r="F24">
-        <v>-1.983566483253661</v>
+        <v>-1.777335306285293</v>
       </c>
       <c r="G24">
-        <v>-5.060259392173903</v>
+        <v>-4.892083678778928</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.242976023056314</v>
       </c>
       <c r="E25">
-        <v>-26.95989621803044</v>
+        <v>-26.11945219847289</v>
       </c>
       <c r="F25">
-        <v>-1.841035931193173</v>
+        <v>-1.878471510860488</v>
       </c>
       <c r="G25">
-        <v>-4.708692698085461</v>
+        <v>-4.522805566055384</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-6.022823706067316</v>
       </c>
       <c r="E26">
-        <v>-27.1282512962136</v>
+        <v>-26.69842212882755</v>
       </c>
       <c r="F26">
-        <v>-1.798380808520818</v>
+        <v>-2.043054031550902</v>
       </c>
       <c r="G26">
-        <v>-5.054422900388168</v>
+        <v>-4.916935944142236</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-6.675681350829443</v>
       </c>
       <c r="E27">
-        <v>-27.2074814774518</v>
+        <v>-26.17339990932627</v>
       </c>
       <c r="F27">
-        <v>-1.598805563633944</v>
+        <v>-1.515078328395984</v>
       </c>
       <c r="G27">
-        <v>-6.083727787821748</v>
+        <v>-5.764399186194728</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.155672310468349</v>
       </c>
       <c r="E28">
-        <v>-27.36477802210823</v>
+        <v>-26.05561430038676</v>
       </c>
       <c r="F28">
-        <v>-1.796439115328656</v>
+        <v>-1.437944897684308</v>
       </c>
       <c r="G28">
-        <v>-5.99450527499285</v>
+        <v>-5.551120600372721</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.430693510037186</v>
       </c>
       <c r="E29">
-        <v>-27.05820938873696</v>
+        <v>-26.95261443182611</v>
       </c>
       <c r="F29">
-        <v>-1.652149939272024</v>
+        <v>-1.475718451251965</v>
       </c>
       <c r="G29">
-        <v>-5.709238876419391</v>
+        <v>-5.987973568643868</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.48253878913295</v>
       </c>
       <c r="E30">
-        <v>-26.5181481070562</v>
+        <v>-26.29631627931646</v>
       </c>
       <c r="F30">
-        <v>-1.405549105295625</v>
+        <v>-1.866039372879273</v>
       </c>
       <c r="G30">
-        <v>-6.438383220898332</v>
+        <v>-5.139556889476067</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.310028719291757</v>
       </c>
       <c r="E31">
-        <v>-26.40312939573538</v>
+        <v>-25.77474928548303</v>
       </c>
       <c r="F31">
-        <v>-1.517124395880899</v>
+        <v>-1.66977262739918</v>
       </c>
       <c r="G31">
-        <v>-5.928744598400767</v>
+        <v>-5.678421007994316</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.928489309106928</v>
       </c>
       <c r="E32">
-        <v>-26.7655793983613</v>
+        <v>-25.75370546676939</v>
       </c>
       <c r="F32">
-        <v>-1.76477642809145</v>
+        <v>-1.998440648338329</v>
       </c>
       <c r="G32">
-        <v>-6.179909067374194</v>
+        <v>-5.451681744009632</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.370462225394821</v>
       </c>
       <c r="E33">
-        <v>-25.88589162305328</v>
+        <v>-25.43827460976511</v>
       </c>
       <c r="F33">
-        <v>-2.006562790722778</v>
+        <v>-1.862895718585649</v>
       </c>
       <c r="G33">
-        <v>-6.072385858804205</v>
+        <v>-5.869879788166987</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.675923235694202</v>
       </c>
       <c r="E34">
-        <v>-25.81524742853362</v>
+        <v>-25.69411527730245</v>
       </c>
       <c r="F34">
-        <v>-1.823223546930775</v>
+        <v>-1.955064017658136</v>
       </c>
       <c r="G34">
-        <v>-5.966855598648857</v>
+        <v>-5.62376059059541</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.894826627930938</v>
       </c>
       <c r="E35">
-        <v>-25.54240234109748</v>
+        <v>-25.03314373961689</v>
       </c>
       <c r="F35">
-        <v>-1.674263207089757</v>
+        <v>-1.836569374157278</v>
       </c>
       <c r="G35">
-        <v>-6.253562084531899</v>
+        <v>-5.228302683747309</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.074335659176727</v>
       </c>
       <c r="E36">
-        <v>-24.65491653354825</v>
+        <v>-25.37912368227692</v>
       </c>
       <c r="F36">
-        <v>-2.069423451084219</v>
+        <v>-2.035959893113327</v>
       </c>
       <c r="G36">
-        <v>-5.716912720979422</v>
+        <v>-4.799259292403303</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.263675712353696</v>
       </c>
       <c r="E37">
-        <v>-24.64536598186607</v>
+        <v>-24.15556170472244</v>
       </c>
       <c r="F37">
-        <v>-2.260466511722258</v>
+        <v>-2.137120948710606</v>
       </c>
       <c r="G37">
-        <v>-4.776707856189788</v>
+        <v>-4.571179257475214</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.502759180066733</v>
       </c>
       <c r="E38">
-        <v>-25.25025689744064</v>
+        <v>-23.88337777449141</v>
       </c>
       <c r="F38">
-        <v>-2.188118559496554</v>
+        <v>-2.293906047038468</v>
       </c>
       <c r="G38">
-        <v>-4.655720658911583</v>
+        <v>-3.984216222816893</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.827290427761369</v>
       </c>
       <c r="E39">
-        <v>-23.28638904606023</v>
+        <v>-23.3968928687954</v>
       </c>
       <c r="F39">
-        <v>-2.397576227498826</v>
+        <v>-2.426131708608131</v>
       </c>
       <c r="G39">
-        <v>-3.361555575608612</v>
+        <v>-4.120746431401976</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.263911241023605</v>
       </c>
       <c r="E40">
-        <v>-23.14690298967597</v>
+        <v>-22.54896781017718</v>
       </c>
       <c r="F40">
-        <v>-2.468564000449132</v>
+        <v>-2.31097704247536</v>
       </c>
       <c r="G40">
-        <v>-3.494583227013146</v>
+        <v>-3.456468916219516</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.8303975894688836</v>
       </c>
       <c r="E41">
-        <v>-23.58587967455751</v>
+        <v>-23.01247976723228</v>
       </c>
       <c r="F41">
-        <v>-2.591411714651702</v>
+        <v>-2.682158535260985</v>
       </c>
       <c r="G41">
-        <v>-3.411491844522978</v>
+        <v>-3.261487715593061</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.535563873303928</v>
       </c>
       <c r="E42">
-        <v>-22.33824885765226</v>
+        <v>-21.71781621928337</v>
       </c>
       <c r="F42">
-        <v>-2.801448411468531</v>
+        <v>-3.028712665161381</v>
       </c>
       <c r="G42">
-        <v>-3.03768821604725</v>
+        <v>-4.085489121408738</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.3755728281025205</v>
       </c>
       <c r="E43">
-        <v>-21.83079258882673</v>
+        <v>-22.24214558226148</v>
       </c>
       <c r="F43">
-        <v>-3.229169292964833</v>
+        <v>-2.85723398584266</v>
       </c>
       <c r="G43">
-        <v>-3.280765022268237</v>
+        <v>-3.108848392413885</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.3401679684790512</v>
       </c>
       <c r="E44">
-        <v>-22.49627901509794</v>
+        <v>-22.13736575067201</v>
       </c>
       <c r="F44">
-        <v>-3.062405680902847</v>
+        <v>-2.964470287972071</v>
       </c>
       <c r="G44">
-        <v>-3.376853606545584</v>
+        <v>-2.70836838798271</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.4079711414481603</v>
       </c>
       <c r="E45">
-        <v>-21.37899579402947</v>
+        <v>-21.27077885066818</v>
       </c>
       <c r="F45">
-        <v>-3.251625504887325</v>
+        <v>-3.061910317195974</v>
       </c>
       <c r="G45">
-        <v>-2.782186932417379</v>
+        <v>-2.377058922049067</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.5554088790033448</v>
       </c>
       <c r="E46">
-        <v>-21.24009843926621</v>
+        <v>-20.70312557685868</v>
       </c>
       <c r="F46">
-        <v>-3.06011607340151</v>
+        <v>-3.014405103380227</v>
       </c>
       <c r="G46">
-        <v>-3.179753656773995</v>
+        <v>-3.287995253726006</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.7506529872211259</v>
       </c>
       <c r="E47">
-        <v>-20.57943483781317</v>
+        <v>-20.60944503506201</v>
       </c>
       <c r="F47">
-        <v>-3.273286484103129</v>
+        <v>-3.468698354423533</v>
       </c>
       <c r="G47">
-        <v>-3.084671478340587</v>
+        <v>-3.482241513242743</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.9651354057707009</v>
       </c>
       <c r="E48">
-        <v>-20.17071741625088</v>
+        <v>-19.73954782055857</v>
       </c>
       <c r="F48">
-        <v>-3.80809538996374</v>
+        <v>-3.107241894946774</v>
       </c>
       <c r="G48">
-        <v>-2.583799180431014</v>
+        <v>-3.128297847457103</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.169839207187225</v>
       </c>
       <c r="E49">
-        <v>-20.22517231619312</v>
+        <v>-19.53292713701059</v>
       </c>
       <c r="F49">
-        <v>-3.742895420056794</v>
+        <v>-3.419907514398641</v>
       </c>
       <c r="G49">
-        <v>-3.10659722144718</v>
+        <v>-2.361962834389991</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.343007004581253</v>
       </c>
       <c r="E50">
-        <v>-19.34758575282466</v>
+        <v>-19.18780307593802</v>
       </c>
       <c r="F50">
-        <v>-3.600396345957612</v>
+        <v>-3.439254863458427</v>
       </c>
       <c r="G50">
-        <v>-3.113234865253419</v>
+        <v>-2.608512402881673</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.467935416597555</v>
       </c>
       <c r="E51">
-        <v>-19.06649884269455</v>
+        <v>-17.89439391528924</v>
       </c>
       <c r="F51">
-        <v>-3.49794138047716</v>
+        <v>-3.384730064271358</v>
       </c>
       <c r="G51">
-        <v>-2.808330310541003</v>
+        <v>-3.048702401056406</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.5360766174981</v>
       </c>
       <c r="E52">
-        <v>-18.25373285627188</v>
+        <v>-18.11771108250349</v>
       </c>
       <c r="F52">
-        <v>-3.852123117422534</v>
+        <v>-3.468870654843315</v>
       </c>
       <c r="G52">
-        <v>-3.048891102152144</v>
+        <v>-2.77568502097825</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.546237429558446</v>
       </c>
       <c r="E53">
-        <v>-17.30734971577889</v>
+        <v>-18.09549891749587</v>
       </c>
       <c r="F53">
-        <v>-3.738610275482112</v>
+        <v>-3.40769240867696</v>
       </c>
       <c r="G53">
-        <v>-3.310199082657897</v>
+        <v>-3.195621101543722</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.503371854383865</v>
       </c>
       <c r="E54">
-        <v>-17.32450357531995</v>
+        <v>-16.76522797842465</v>
       </c>
       <c r="F54">
-        <v>-3.88116153672767</v>
+        <v>-3.563293769986222</v>
       </c>
       <c r="G54">
-        <v>-3.389284705045547</v>
+        <v>-3.276107084694483</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.418880718627437</v>
       </c>
       <c r="E55">
-        <v>-16.8046392877134</v>
+        <v>-16.15005742685267</v>
       </c>
       <c r="F55">
-        <v>-3.669905483093921</v>
+        <v>-3.581974283286753</v>
       </c>
       <c r="G55">
-        <v>-3.178105005095438</v>
+        <v>-3.001570164213802</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.307173374923988</v>
       </c>
       <c r="E56">
-        <v>-16.4152810925339</v>
+        <v>-16.949636496965</v>
       </c>
       <c r="F56">
-        <v>-3.883600250361512</v>
+        <v>-3.627995891084085</v>
       </c>
       <c r="G56">
-        <v>-3.569398245655135</v>
+        <v>-3.426352883448766</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.186698346348094</v>
       </c>
       <c r="E57">
-        <v>-15.98354996606463</v>
+        <v>-15.24598381901334</v>
       </c>
       <c r="F57">
-        <v>-3.940025324370604</v>
+        <v>-3.559038446638041</v>
       </c>
       <c r="G57">
-        <v>-3.54784328364894</v>
+        <v>-4.277808643421619</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.074213253755193</v>
       </c>
       <c r="E58">
-        <v>-15.48845643128004</v>
+        <v>-15.80399597166051</v>
       </c>
       <c r="F58">
-        <v>-3.933164785540618</v>
+        <v>-3.564153615350328</v>
       </c>
       <c r="G58">
-        <v>-3.249827974203748</v>
+        <v>-3.855376411519537</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.9867573800439521</v>
       </c>
       <c r="E59">
-        <v>-15.20316709727082</v>
+        <v>-15.09256364810748</v>
       </c>
       <c r="F59">
-        <v>-4.003716837237052</v>
+        <v>-3.60688494782374</v>
       </c>
       <c r="G59">
-        <v>-3.76347235680383</v>
+        <v>-4.241081451208945</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.9362476638219066</v>
       </c>
       <c r="E60">
-        <v>-15.31142479689819</v>
+        <v>-14.72478363157453</v>
       </c>
       <c r="F60">
-        <v>-3.830515153720509</v>
+        <v>-3.925512327473556</v>
       </c>
       <c r="G60">
-        <v>-4.273415549491006</v>
+        <v>-3.727920408257597</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.932681200666952</v>
       </c>
       <c r="E61">
-        <v>-14.63595308544007</v>
+        <v>-14.04044063953538</v>
       </c>
       <c r="F61">
-        <v>-3.774104990324668</v>
+        <v>-3.701454683996943</v>
       </c>
       <c r="G61">
-        <v>-4.703647426683611</v>
+        <v>-4.583554076701009</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.979422614543433</v>
       </c>
       <c r="E62">
-        <v>-13.55844798005498</v>
+        <v>-14.1896402726661</v>
       </c>
       <c r="F62">
-        <v>-4.116127950531751</v>
+        <v>-3.727316314312344</v>
       </c>
       <c r="G62">
-        <v>-4.826955316384845</v>
+        <v>-4.693493983514666</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.078110953024519</v>
       </c>
       <c r="E63">
-        <v>-13.67725249564621</v>
+        <v>-13.56362855431976</v>
       </c>
       <c r="F63">
-        <v>-3.966913301898073</v>
+        <v>-3.956246414852223</v>
       </c>
       <c r="G63">
-        <v>-5.078043642810869</v>
+        <v>-4.561995804149276</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.224529042642706</v>
       </c>
       <c r="E64">
-        <v>-12.52195273528336</v>
+        <v>-13.63098960518385</v>
       </c>
       <c r="F64">
-        <v>-4.191149044366288</v>
+        <v>-3.987411253280346</v>
       </c>
       <c r="G64">
-        <v>-5.971377803855502</v>
+        <v>-5.134107731518426</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.412957874907335</v>
       </c>
       <c r="E65">
-        <v>-12.51223010158889</v>
+        <v>-13.57454217667824</v>
       </c>
       <c r="F65">
-        <v>-4.29841268261999</v>
+        <v>-3.826506683858362</v>
       </c>
       <c r="G65">
-        <v>-5.677364943967288</v>
+        <v>-5.102710517623978</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.632978209760767</v>
       </c>
       <c r="E66">
-        <v>-13.27864715654305</v>
+        <v>-13.35316319633927</v>
       </c>
       <c r="F66">
-        <v>-4.58221715339092</v>
+        <v>-4.048540625769936</v>
       </c>
       <c r="G66">
-        <v>-5.562419492298254</v>
+        <v>-5.561373359907844</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.873247773122254</v>
       </c>
       <c r="E67">
-        <v>-12.76366456391677</v>
+        <v>-13.31906831553552</v>
       </c>
       <c r="F67">
-        <v>-4.70563312763181</v>
+        <v>-4.183897516122181</v>
       </c>
       <c r="G67">
-        <v>-6.089514621424394</v>
+        <v>-5.478881186160285</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.12104367211369</v>
       </c>
       <c r="E68">
-        <v>-12.91866970072532</v>
+        <v>-13.65634905962681</v>
       </c>
       <c r="F68">
-        <v>-4.613730734495622</v>
+        <v>-4.014910565951082</v>
       </c>
       <c r="G68">
-        <v>-5.800067003834836</v>
+        <v>-6.041895734387517</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.36413671341678</v>
       </c>
       <c r="E69">
-        <v>-13.31660935414935</v>
+        <v>-13.33598669442818</v>
       </c>
       <c r="F69">
-        <v>-4.723698992319465</v>
+        <v>-3.995389259736708</v>
       </c>
       <c r="G69">
-        <v>-6.188549591231692</v>
+        <v>-5.511933672824368</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.593131721444838</v>
       </c>
       <c r="E70">
-        <v>-13.19641459703777</v>
+        <v>-13.56741435859017</v>
       </c>
       <c r="F70">
-        <v>-4.628461592019605</v>
+        <v>-4.435620145750089</v>
       </c>
       <c r="G70">
-        <v>-5.636122167639048</v>
+        <v>-5.563564941054842</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.799519084684914</v>
       </c>
       <c r="E71">
-        <v>-13.00569791420473</v>
+        <v>-12.53044815252175</v>
       </c>
       <c r="F71">
-        <v>-5.078468041753423</v>
+        <v>-4.439361052941131</v>
       </c>
       <c r="G71">
-        <v>-5.892987396031099</v>
+        <v>-5.577141488311392</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.980296733235216</v>
       </c>
       <c r="E72">
-        <v>-12.95327177061793</v>
+        <v>-12.95710738810243</v>
       </c>
       <c r="F72">
-        <v>-4.804505404095154</v>
+        <v>-4.225315886262156</v>
       </c>
       <c r="G72">
-        <v>-6.277639682239019</v>
+        <v>-5.10688180500346</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.132481419385519</v>
       </c>
       <c r="E73">
-        <v>-13.14771085908527</v>
+        <v>-12.38873408692571</v>
       </c>
       <c r="F73">
-        <v>-4.838910815803028</v>
+        <v>-4.718970671184285</v>
       </c>
       <c r="G73">
-        <v>-6.208306927010062</v>
+        <v>-4.950567776275692</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.260114060330344</v>
       </c>
       <c r="E74">
-        <v>-13.63132924073443</v>
+        <v>-13.70498034199518</v>
       </c>
       <c r="F74">
-        <v>-5.098338090644375</v>
+        <v>-4.462093111208755</v>
       </c>
       <c r="G74">
-        <v>-5.881658709195714</v>
+        <v>-5.62970633038394</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.365003099438407</v>
       </c>
       <c r="E75">
-        <v>-13.58339987183725</v>
+        <v>-13.28339299730309</v>
       </c>
       <c r="F75">
-        <v>-4.644580793310681</v>
+        <v>-4.605117370241312</v>
       </c>
       <c r="G75">
-        <v>-5.175443203121766</v>
+        <v>-5.50683874323943</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.455113577984191</v>
       </c>
       <c r="E76">
-        <v>-13.58398857345824</v>
+        <v>-12.9242034959627</v>
       </c>
       <c r="F76">
-        <v>-5.057872343017618</v>
+        <v>-4.707909481254704</v>
       </c>
       <c r="G76">
-        <v>-5.43933671969369</v>
+        <v>-5.139172866193511</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.534302171048643</v>
       </c>
       <c r="E77">
-        <v>-13.48853739832457</v>
+        <v>-14.11030593652572</v>
       </c>
       <c r="F77">
-        <v>-5.21226925812321</v>
+        <v>-4.733500235429388</v>
       </c>
       <c r="G77">
-        <v>-4.981167148695175</v>
+        <v>-4.796968394890126</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.610561851380314</v>
       </c>
       <c r="E78">
-        <v>-15.18694157490133</v>
+        <v>-14.13829190589312</v>
       </c>
       <c r="F78">
-        <v>-5.027912779160569</v>
+        <v>-5.203659207338512</v>
       </c>
       <c r="G78">
-        <v>-4.493109972568121</v>
+        <v>-4.47435242154261</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.686500607143942</v>
       </c>
       <c r="E79">
-        <v>-14.82960421943007</v>
+        <v>-14.39405558937234</v>
       </c>
       <c r="F79">
-        <v>-5.305715728098217</v>
+        <v>-5.291824006753269</v>
       </c>
       <c r="G79">
-        <v>-4.771235524413372</v>
+        <v>-5.030255917951489</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.767113500392591</v>
       </c>
       <c r="E80">
-        <v>-14.99190925633899</v>
+        <v>-15.21469206362034</v>
       </c>
       <c r="F80">
-        <v>-5.533091811390444</v>
+        <v>-5.096680527471372</v>
       </c>
       <c r="G80">
-        <v>-4.926582873843673</v>
+        <v>-4.728039526216961</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.851250498288922</v>
       </c>
       <c r="E81">
-        <v>-16.37274966465386</v>
+        <v>-15.95128911723399</v>
       </c>
       <c r="F81">
-        <v>-5.754273363244538</v>
+        <v>-5.098570033517158</v>
       </c>
       <c r="G81">
-        <v>-4.808793663556403</v>
+        <v>-4.549336278007103</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.939719086671559</v>
       </c>
       <c r="E82">
-        <v>-17.08746060338845</v>
+        <v>-17.1625291170136</v>
       </c>
       <c r="F82">
-        <v>-5.689582839290313</v>
+        <v>-5.33968873202183</v>
       </c>
       <c r="G82">
-        <v>-4.981676972708224</v>
+        <v>-4.582272895577312</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.027892456933777</v>
       </c>
       <c r="E83">
-        <v>-17.61856456348203</v>
+        <v>-17.50276242615789</v>
       </c>
       <c r="F83">
-        <v>-6.044985589787413</v>
+        <v>-5.221026758305607</v>
       </c>
       <c r="G83">
-        <v>-5.060461335451799</v>
+        <v>-4.218722026636708</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.114492388252278</v>
       </c>
       <c r="E84">
-        <v>-18.65308539358631</v>
+        <v>-18.47039316669487</v>
       </c>
       <c r="F84">
-        <v>-5.537416717600461</v>
+        <v>-5.720408047083288</v>
       </c>
       <c r="G84">
-        <v>-4.726698755273556</v>
+        <v>-3.891924834273091</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.19525919801488</v>
       </c>
       <c r="E85">
-        <v>-20.09380581370461</v>
+        <v>-19.73547672242567</v>
       </c>
       <c r="F85">
-        <v>-6.328710537287675</v>
+        <v>-5.547090392130354</v>
       </c>
       <c r="G85">
-        <v>-4.366124066772756</v>
+        <v>-4.595875927198177</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.269635177159384</v>
       </c>
       <c r="E86">
-        <v>-20.61698041581077</v>
+        <v>-21.39730894291649</v>
       </c>
       <c r="F86">
-        <v>-6.222794652798327</v>
+        <v>-5.747692812596698</v>
       </c>
       <c r="G86">
-        <v>-4.120021421928876</v>
+        <v>-4.157678877438086</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.334707996778012</v>
       </c>
       <c r="E87">
-        <v>-22.09280103796252</v>
+        <v>-22.22335241512965</v>
       </c>
       <c r="F87">
-        <v>-6.183684942609954</v>
+        <v>-5.907079812936754</v>
       </c>
       <c r="G87">
-        <v>-4.353699589363872</v>
+        <v>-4.376201367394298</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.391080182052213</v>
       </c>
       <c r="E88">
-        <v>-22.93452661566424</v>
+        <v>-23.00926002221282</v>
       </c>
       <c r="F88">
-        <v>-6.106163835953768</v>
+        <v>-5.986622964423174</v>
       </c>
       <c r="G88">
-        <v>-4.119415592095189</v>
+        <v>-4.208634794378548</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.438838068642694</v>
       </c>
       <c r="E89">
-        <v>-25.29152035259853</v>
+        <v>-24.22739235943211</v>
       </c>
       <c r="F89">
-        <v>-6.098973606897468</v>
+        <v>-6.067165955364772</v>
       </c>
       <c r="G89">
-        <v>-4.917065055418267</v>
+        <v>-4.275004611349857</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.48103727756802</v>
       </c>
       <c r="E90">
-        <v>-26.85296083281331</v>
+        <v>-26.09558261197846</v>
       </c>
       <c r="F90">
-        <v>-6.424604004570551</v>
+        <v>-6.245003182867382</v>
       </c>
       <c r="G90">
-        <v>-4.246818626628501</v>
+        <v>-3.628481551894508</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.521184630862699</v>
       </c>
       <c r="E91">
-        <v>-28.9579766905388</v>
+        <v>-28.68425760761917</v>
       </c>
       <c r="F91">
-        <v>-6.207917174244048</v>
+        <v>-6.225782574020225</v>
       </c>
       <c r="G91">
-        <v>-4.87962609591465</v>
+        <v>-4.650499928596152</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.563468072821836</v>
       </c>
       <c r="E92">
-        <v>-30.17408479987665</v>
+        <v>-30.18772909206176</v>
       </c>
       <c r="F92">
-        <v>-6.571881930216484</v>
+        <v>-6.43944876261242</v>
       </c>
       <c r="G92">
-        <v>-5.139000717825469</v>
+        <v>-4.859944902683683</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.614685000715832</v>
       </c>
       <c r="E93">
-        <v>-32.91634751996151</v>
+        <v>-32.01727561166366</v>
       </c>
       <c r="F93">
-        <v>-6.272991232305769</v>
+        <v>-6.305422644492772</v>
       </c>
       <c r="G93">
-        <v>-5.426180611720627</v>
+        <v>-5.269022393880345</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.679981449245732</v>
       </c>
       <c r="E94">
-        <v>-34.94987009429091</v>
+        <v>-33.94983132951803</v>
       </c>
       <c r="F94">
-        <v>-6.339454462501984</v>
+        <v>-6.261215989674974</v>
       </c>
       <c r="G94">
-        <v>-6.170282000945994</v>
+        <v>-4.659176868454582</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.767216371257779</v>
       </c>
       <c r="E95">
-        <v>-37.39456452309474</v>
+        <v>-35.94950356064009</v>
       </c>
       <c r="F95">
-        <v>-6.411237053975277</v>
+        <v>-6.412314759966319</v>
       </c>
       <c r="G95">
-        <v>-6.398623568971685</v>
+        <v>-5.949121006194981</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.885103817594717</v>
       </c>
       <c r="E96">
-        <v>-38.71096927475448</v>
+        <v>-38.27426361958779</v>
       </c>
       <c r="F96">
-        <v>-6.445016634110337</v>
+        <v>-6.474165226280046</v>
       </c>
       <c r="G96">
-        <v>-6.712777787920824</v>
+        <v>-6.290663368390511</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.036897760107079</v>
       </c>
       <c r="E97">
-        <v>-41.92806740115062</v>
+        <v>-40.89464019751919</v>
       </c>
       <c r="F97">
-        <v>-6.450328954264489</v>
+        <v>-6.91911987740789</v>
       </c>
       <c r="G97">
-        <v>-7.317015249203061</v>
+        <v>-6.140629444550742</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.238335934227441</v>
       </c>
       <c r="E98">
-        <v>-43.89073973539301</v>
+        <v>-44.22698572317354</v>
       </c>
       <c r="F98">
-        <v>-6.378920370673561</v>
+        <v>-6.676542009723187</v>
       </c>
       <c r="G98">
-        <v>-6.851069206732799</v>
+        <v>-6.604109130594247</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.479897357465198</v>
       </c>
       <c r="E99">
-        <v>-46.95359350861388</v>
+        <v>-46.57819886303704</v>
       </c>
       <c r="F99">
-        <v>-6.328558946052962</v>
+        <v>-6.58335564711266</v>
       </c>
       <c r="G99">
-        <v>-7.988969919491091</v>
+        <v>-7.428818993155327</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.790082360787969</v>
       </c>
       <c r="E100">
-        <v>-48.61684993418012</v>
+        <v>-48.60946172883661</v>
       </c>
       <c r="F100">
-        <v>-6.3284810795171</v>
+        <v>-6.479645705016967</v>
       </c>
       <c r="G100">
-        <v>-9.283909670450251</v>
+        <v>-7.624114695608013</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.126340500098375</v>
       </c>
       <c r="E101">
-        <v>-51.573136260697</v>
+        <v>-50.23772663574557</v>
       </c>
       <c r="F101">
-        <v>-5.886233947245305</v>
+        <v>-6.800331991846441</v>
       </c>
       <c r="G101">
-        <v>-8.736265985161856</v>
+        <v>-8.200798486366898</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-6.560083017304514</v>
       </c>
       <c r="E102">
-        <v>-53.17724515513055</v>
+        <v>-53.54672334941638</v>
       </c>
       <c r="F102">
-        <v>-6.041221488309092</v>
+        <v>-6.878369585578272</v>
       </c>
       <c r="G102">
-        <v>-9.380402141283389</v>
+        <v>-7.936928143613748</v>
       </c>
     </row>
   </sheetData>
